--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_04/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_04/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>55.38</v>
+        <v>54.49</v>
       </c>
       <c r="D2" t="n">
-        <v>23.13</v>
+        <v>21.82</v>
       </c>
       <c r="E2" t="n">
-        <v>41.77</v>
+        <v>40.04</v>
       </c>
       <c r="F2" t="n">
-        <v>30.41</v>
+        <v>31.81</v>
       </c>
       <c r="G2" t="n">
-        <v>34.89</v>
+        <v>35.88</v>
       </c>
       <c r="H2" t="n">
-        <v>45.39</v>
+        <v>45.92</v>
       </c>
       <c r="I2" t="n">
-        <v>76.01000000000001</v>
+        <v>72.61</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>69.59</v>
+        <v>68.19</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>38.86</v>
+        <v>38.7</v>
       </c>
       <c r="D3" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6</v>
+        <v>0.97</v>
       </c>
       <c r="F3" t="n">
-        <v>38.78</v>
+        <v>38.57</v>
       </c>
       <c r="G3" t="n">
-        <v>38.78</v>
+        <v>38.57</v>
       </c>
       <c r="H3" t="n">
-        <v>38.79</v>
+        <v>38.57</v>
       </c>
       <c r="I3" t="n">
-        <v>38.79</v>
+        <v>38.58</v>
       </c>
       <c r="J3" t="n">
-        <v>39.89</v>
+        <v>40.36</v>
       </c>
       <c r="K3" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>6.91</v>
+        <v>7.38</v>
       </c>
       <c r="D4" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="E4" t="n">
-        <v>27.26</v>
+        <v>25.27</v>
       </c>
       <c r="F4" t="n">
-        <v>5.02</v>
+        <v>5.24</v>
       </c>
       <c r="G4" t="n">
-        <v>5.14</v>
+        <v>5.64</v>
       </c>
       <c r="H4" t="n">
-        <v>6.03</v>
+        <v>7.23</v>
       </c>
       <c r="I4" t="n">
-        <v>8.31</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>10.8</v>
+        <v>11.5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.78</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>93.89</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>36.33</v>
+        <v>20.3</v>
       </c>
       <c r="E5" t="n">
-        <v>38.7</v>
+        <v>25.28</v>
       </c>
       <c r="F5" t="n">
-        <v>58.63</v>
+        <v>57.98</v>
       </c>
       <c r="G5" t="n">
-        <v>70.72</v>
+        <v>62.6</v>
       </c>
       <c r="H5" t="n">
-        <v>73.89</v>
+        <v>76.98</v>
       </c>
       <c r="I5" t="n">
-        <v>114.3</v>
+        <v>100.31</v>
       </c>
       <c r="J5" t="n">
-        <v>194.42</v>
+        <v>118.18</v>
       </c>
       <c r="K5" t="n">
-        <v>135.79</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>4.26</v>
+        <v>3.22</v>
       </c>
       <c r="D6" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="E6" t="n">
-        <v>19.14</v>
+        <v>26.7</v>
       </c>
       <c r="F6" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>4.27</v>
+        <v>2.62</v>
       </c>
       <c r="H6" t="n">
-        <v>4.55</v>
+        <v>2.88</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.09</v>
       </c>
       <c r="J6" t="n">
-        <v>4.99</v>
+        <v>4.65</v>
       </c>
       <c r="K6" t="n">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
     </row>
   </sheetData>
